--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/SOUTH_DAKOTA_2013.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2013/SOUTH_DAKOTA_2013.xlsx
@@ -2274,7 +2274,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C107">
